--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.8291,0.0836,0.0341,0.0623</t>
-  </si>
-  <si>
-    <t>0.0086,0.0052,0.0039,0.9934</t>
-  </si>
-  <si>
-    <t>0.8399,0.0058,0.0018,0.1900</t>
-  </si>
-  <si>
-    <t>0.0542,0.0072,0.0072,0.9716</t>
-  </si>
-  <si>
-    <t>0.9916,0.0023,0.0007,0.0030</t>
-  </si>
-  <si>
-    <t>0.9837,0.0060,0.0035,0.0050</t>
-  </si>
-  <si>
-    <t>0.9874,0.0038,0.0044,0.0028</t>
-  </si>
-  <si>
-    <t>0.9835,0.0038,0.0032,0.0067</t>
-  </si>
-  <si>
-    <t>0.9789,0.0119,0.0028,0.0064</t>
-  </si>
-  <si>
-    <t>0.9916,0.0038,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9898,0.0041,0.0006,0.0034</t>
-  </si>
-  <si>
-    <t>0.9855,0.0046,0.0029,0.0046</t>
-  </si>
-  <si>
-    <t>0.7202,0.0155,0.4022,0.0018</t>
-  </si>
-  <si>
-    <t>0.0592,0.0989,0.8638,0.0105</t>
-  </si>
-  <si>
-    <t>0.4556,0.0488,0.4712,0.0016</t>
-  </si>
-  <si>
-    <t>0.0453,0.0297,0.9113,0.0056</t>
-  </si>
-  <si>
-    <t>0.4453,0.2902,0.2967,0.1086</t>
-  </si>
-  <si>
-    <t>0.0049,0.9930,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.0116,0.9839,0.0093,0.0022</t>
-  </si>
-  <si>
-    <t>0.3283,0.7504,0.0248,0.0099</t>
-  </si>
-  <si>
-    <t>0.0388,0.9601,0.0100,0.0043</t>
-  </si>
-  <si>
-    <t>0.0078,0.9901,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.2857,0.0585,0.6229,0.0279</t>
-  </si>
-  <si>
-    <t>0.1374,0.1618,0.6860,0.0299</t>
-  </si>
-  <si>
-    <t>0.0051,0.0467,0.9796,0.0078</t>
-  </si>
-  <si>
-    <t>0.0290,0.0373,0.9266,0.0122</t>
-  </si>
-  <si>
-    <t>0.0372,0.0098,0.9686,0.0027</t>
-  </si>
-  <si>
-    <t>0.0399,0.0086,0.9608,0.0030</t>
-  </si>
-  <si>
-    <t>0.0084,0.0034,0.9836,0.0080</t>
-  </si>
-  <si>
-    <t>0.3475,0.7796,0.0049,0.0046</t>
-  </si>
-  <si>
-    <t>0.4114,0.3233,0.2511,0.0391</t>
-  </si>
-  <si>
-    <t>0.0062,0.0507,0.9801,0.0129</t>
-  </si>
-  <si>
-    <t>0.0115,0.9762,0.0454,0.0009</t>
-  </si>
-  <si>
-    <t>0.8964,0.0357,0.0385,0.0261</t>
-  </si>
-  <si>
-    <t>0.2196,0.0277,0.7643,0.0852</t>
-  </si>
-  <si>
-    <t>0.6808,0.2193,0.1456,0.0228</t>
-  </si>
-  <si>
-    <t>0.0809,0.8590,0.1980,0.0055</t>
-  </si>
-  <si>
-    <t>0.0127,0.7862,0.6992,0.0068</t>
-  </si>
-  <si>
-    <t>0.0276,0.0502,0.9597,0.0025</t>
-  </si>
-  <si>
-    <t>0.0128,0.0712,0.9679,0.0027</t>
-  </si>
-  <si>
-    <t>0.0046,0.0045,0.9808,0.0272</t>
-  </si>
-  <si>
-    <t>0.0069,0.1479,0.9758,0.0028</t>
-  </si>
-  <si>
-    <t>0.0132,0.9746,0.0385,0.0014</t>
-  </si>
-  <si>
-    <t>0.0183,0.0381,0.9689,0.0023</t>
-  </si>
-  <si>
-    <t>0.1647,0.6414,0.0290,0.5727</t>
-  </si>
-  <si>
-    <t>0.0018,0.9903,0.0141,0.0101</t>
-  </si>
-  <si>
-    <t>0.0011,0.9929,0.0339,0.0047</t>
-  </si>
-  <si>
-    <t>0.0004,0.9973,0.0134,0.0034</t>
-  </si>
-  <si>
-    <t>0.0031,0.0425,0.9920,0.0004</t>
-  </si>
-  <si>
-    <t>0.0020,0.2976,0.9850,0.0009</t>
-  </si>
-  <si>
-    <t>0.0410,0.0046,0.9639,0.0050</t>
-  </si>
-  <si>
-    <t>0.0089,0.0044,0.9902,0.0017</t>
-  </si>
-  <si>
-    <t>0.0050,0.0202,0.9871,0.0042</t>
-  </si>
-  <si>
-    <t>0.0316,0.4069,0.8479,0.0044</t>
-  </si>
-  <si>
-    <t>0.9497,0.0476,0.0093,0.0055</t>
-  </si>
-  <si>
-    <t>0.9764,0.0046,0.0053,0.0097</t>
-  </si>
-  <si>
-    <t>0.9715,0.0199,0.0036,0.0068</t>
-  </si>
-  <si>
-    <t>0.0247,0.0208,0.9769,0.0041</t>
-  </si>
-  <si>
-    <t>0.9816,0.0045,0.0008,0.0088</t>
-  </si>
-  <si>
-    <t>0.9930,0.0033,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9836,0.0140,0.0024,0.0017</t>
-  </si>
-  <si>
-    <t>0.0002,0.9853,0.9309,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.1979,0.9805,0.0007</t>
-  </si>
-  <si>
-    <t>0.0041,0.0174,0.9891,0.0026</t>
-  </si>
-  <si>
-    <t>0.0004,0.9743,0.9560,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0088,0.9965,0.0030</t>
-  </si>
-  <si>
-    <t>0.0164,0.9806,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.0125,0.9848,0.0080,0.0022</t>
-  </si>
-  <si>
-    <t>0.8800,0.0094,0.1645,0.0093</t>
-  </si>
-  <si>
-    <t>0.7872,0.0908,0.1174,0.0243</t>
-  </si>
-  <si>
-    <t>0.0094,0.1557,0.9767,0.0029</t>
-  </si>
-  <si>
-    <t>0.0005,0.9821,0.8160,0.0010</t>
-  </si>
-  <si>
-    <t>0.0015,0.9396,0.7544,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9931,0.6779,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9602,0.8311,0.0007</t>
-  </si>
-  <si>
-    <t>0.0123,0.0057,0.0175,0.9857</t>
-  </si>
-  <si>
-    <t>0.0014,0.0080,0.0038,0.9971</t>
-  </si>
-  <si>
-    <t>0.0023,0.0052,0.0012,0.9978</t>
-  </si>
-  <si>
-    <t>0.0017,0.0017,0.0081,0.9965</t>
-  </si>
-  <si>
-    <t>0.0021,0.0070,0.0061,0.9961</t>
-  </si>
-  <si>
-    <t>0.0008,0.0025,0.0011,0.9989</t>
-  </si>
-  <si>
-    <t>0.0012,0.9854,0.4588,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.9209,0.9101,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.9434,0.7794,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.8220,0.9572,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.9607,0.8582,0.0003</t>
-  </si>
-  <si>
-    <t>0.0033,0.7393,0.8738,0.0015</t>
-  </si>
-  <si>
-    <t>0.9921,0.0045,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9845,0.0139,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.9883,0.0098,0.0014,0.0017</t>
-  </si>
-  <si>
-    <t>0.9875,0.0045,0.0007,0.0051</t>
-  </si>
-  <si>
-    <t>0.9810,0.0065,0.0019,0.0061</t>
-  </si>
-  <si>
-    <t>0.9833,0.0055,0.0011,0.0074</t>
-  </si>
-  <si>
-    <t>0.9879,0.0039,0.0005,0.0051</t>
-  </si>
-  <si>
-    <t>0.9867,0.0075,0.0023,0.0033</t>
-  </si>
-  <si>
-    <t>0.9811,0.0021,0.0008,0.0154</t>
-  </si>
-  <si>
-    <t>0.9908,0.0054,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9942,0.0015,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9906,0.0026,0.0010,0.0037</t>
-  </si>
-  <si>
-    <t>0.9841,0.0048,0.0008,0.0064</t>
-  </si>
-  <si>
-    <t>0.9938,0.0023,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9896,0.0044,0.0002,0.0035</t>
-  </si>
-  <si>
-    <t>0.9922,0.0017,0.0007,0.0035</t>
-  </si>
-  <si>
-    <t>0.0095,0.0018,0.9791,0.0216</t>
-  </si>
-  <si>
-    <t>0.0208,0.0272,0.9588,0.0099</t>
-  </si>
-  <si>
-    <t>0.8351,0.0034,0.1764,0.0108</t>
-  </si>
-  <si>
-    <t>0.0135,0.0038,0.9855,0.0024</t>
-  </si>
-  <si>
-    <t>0.0339,0.9757,0.0019,0.0019</t>
-  </si>
-  <si>
-    <t>0.0126,0.9834,0.0111,0.0046</t>
-  </si>
-  <si>
-    <t>0.0637,0.9461,0.0043,0.0043</t>
-  </si>
-  <si>
-    <t>0.2658,0.7667,0.0552,0.0151</t>
-  </si>
-  <si>
-    <t>0.0131,0.9859,0.0040,0.0010</t>
-  </si>
-  <si>
-    <t>0.0024,0.9960,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.7568,0.3819,0.0073,0.0036</t>
-  </si>
-  <si>
-    <t>0.3665,0.6007,0.0459,0.0110</t>
-  </si>
-  <si>
-    <t>0.2833,0.0209,0.7647,0.0088</t>
-  </si>
-  <si>
-    <t>0.8454,0.0403,0.0897,0.0112</t>
-  </si>
-  <si>
-    <t>0.4258,0.0612,0.5350,0.0174</t>
-  </si>
-  <si>
-    <t>0.1400,0.0672,0.1836,0.7916</t>
-  </si>
-  <si>
-    <t>0.0001,0.9987,0.0076,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9968,0.0063,0.0062</t>
-  </si>
-  <si>
-    <t>0.0055,0.9849,0.0247,0.0063</t>
-  </si>
-  <si>
-    <t>0.0001,0.9986,0.0150,0.0009</t>
-  </si>
-  <si>
-    <t>0.0347,0.9554,0.0724,0.0021</t>
-  </si>
-  <si>
-    <t>0.8431,0.1822,0.0211,0.0032</t>
-  </si>
-  <si>
-    <t>0.9180,0.0828,0.0164,0.0048</t>
-  </si>
-  <si>
-    <t>0.9731,0.0162,0.0100,0.0048</t>
-  </si>
-  <si>
-    <t>0.9919,0.0016,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9912,0.0017,0.0012,0.0027</t>
-  </si>
-  <si>
-    <t>0.9815,0.0037,0.0022,0.0091</t>
-  </si>
-  <si>
-    <t>0.9935,0.0015,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9837,0.0043,0.0058,0.0045</t>
-  </si>
-  <si>
-    <t>0.9821,0.0037,0.0016,0.0083</t>
-  </si>
-  <si>
-    <t>0.9791,0.0010,0.0010,0.0156</t>
-  </si>
-  <si>
-    <t>0.0003,0.9865,0.8388,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.4452,0.9186,0.0007</t>
-  </si>
-  <si>
-    <t>0.0039,0.1126,0.9787,0.0029</t>
-  </si>
-  <si>
-    <t>0.0123,0.0840,0.9534,0.0032</t>
-  </si>
-  <si>
-    <t>0.9242,0.0391,0.0189,0.0105</t>
-  </si>
-  <si>
-    <t>0.6647,0.0383,0.2837,0.0232</t>
-  </si>
-  <si>
-    <t>0.6103,0.0043,0.5788,0.0070</t>
-  </si>
-  <si>
-    <t>0.7602,0.1065,0.1182,0.0116</t>
-  </si>
-  <si>
-    <t>0.0104,0.0008,0.0011,0.9949</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.0027,0.9993</t>
-  </si>
-  <si>
-    <t>0.0016,0.0014,0.0035,0.9975</t>
-  </si>
-  <si>
-    <t>0.0023,0.0023,0.0025,0.9975</t>
-  </si>
-  <si>
-    <t>0.0007,0.9659,0.8636,0.0014</t>
-  </si>
-  <si>
-    <t>0.9910,0.0022,0.0009,0.0031</t>
-  </si>
-  <si>
-    <t>0.3604,0.6980,0.0258,0.0263</t>
-  </si>
-  <si>
-    <t>0.9782,0.0038,0.0028,0.0105</t>
-  </si>
-  <si>
-    <t>0.8334,0.2213,0.0264,0.0136</t>
-  </si>
-  <si>
-    <t>0.9845,0.0041,0.0020,0.0059</t>
-  </si>
-  <si>
-    <t>0.1859,0.0066,0.0375,0.8555</t>
-  </si>
-  <si>
-    <t>0.8987,0.0033,0.0031,0.1345</t>
-  </si>
-  <si>
-    <t>0.0017,0.0654,0.9768,0.0234</t>
-  </si>
-  <si>
-    <t>0.6603,0.0059,0.0081,0.4953</t>
-  </si>
-  <si>
-    <t>0.8759,0.0067,0.0036,0.1825</t>
-  </si>
-  <si>
-    <t>0.3311,0.6395,0.1192,0.0477</t>
-  </si>
-  <si>
-    <t>0.9234,0.0410,0.0215,0.0199</t>
-  </si>
-  <si>
-    <t>0.9684,0.0126,0.0115,0.0040</t>
-  </si>
-  <si>
-    <t>0.1738,0.7936,0.0451,0.0674</t>
-  </si>
-  <si>
-    <t>0.9335,0.0535,0.0128,0.0071</t>
-  </si>
-  <si>
-    <t>0.9309,0.0330,0.0280,0.0094</t>
-  </si>
-  <si>
-    <t>0.9827,0.0062,0.0037,0.0049</t>
-  </si>
-  <si>
-    <t>0.9769,0.0057,0.0009,0.0151</t>
-  </si>
-  <si>
-    <t>0.9841,0.0046,0.0015,0.0071</t>
-  </si>
-  <si>
-    <t>0.9863,0.0018,0.0019,0.0069</t>
-  </si>
-  <si>
-    <t>0.9823,0.0055,0.0053,0.0049</t>
-  </si>
-  <si>
-    <t>0.9759,0.0051,0.0080,0.0070</t>
-  </si>
-  <si>
-    <t>0.9830,0.0055,0.0017,0.0066</t>
-  </si>
-  <si>
-    <t>0.9841,0.0031,0.0007,0.0087</t>
-  </si>
-  <si>
-    <t>0.5302,0.4299,0.1210,0.0478</t>
-  </si>
-  <si>
-    <t>0.9180,0.0993,0.0090,0.0064</t>
-  </si>
-  <si>
-    <t>0.8798,0.1054,0.0425,0.0074</t>
-  </si>
-  <si>
-    <t>0.0489,0.0457,0.9619,0.0033</t>
-  </si>
-  <si>
-    <t>0.9730,0.0359,0.0020,0.0025</t>
-  </si>
-  <si>
-    <t>0.9678,0.0071,0.0097,0.0107</t>
-  </si>
-  <si>
-    <t>0.9834,0.0116,0.0024,0.0027</t>
-  </si>
-  <si>
-    <t>0.9194,0.0285,0.0073,0.0421</t>
-  </si>
-  <si>
-    <t>0.0012,0.0573,0.9976,0.0006</t>
-  </si>
-  <si>
-    <t>0.9537,0.0233,0.0208,0.0094</t>
-  </si>
-  <si>
-    <t>0.0007,0.0148,0.9969,0.0010</t>
-  </si>
-  <si>
-    <t>0.0030,0.1233,0.9760,0.0149</t>
-  </si>
-  <si>
-    <t>0.0337,0.0027,0.9438,0.0254</t>
-  </si>
-  <si>
-    <t>0.0041,0.4478,0.9600,0.0014</t>
-  </si>
-  <si>
-    <t>0.0037,0.0347,0.9877,0.0049</t>
-  </si>
-  <si>
-    <t>0.0082,0.0079,0.9853,0.0047</t>
-  </si>
-  <si>
-    <t>0.0023,0.1799,0.9848,0.0011</t>
-  </si>
-  <si>
-    <t>0.1346,0.0271,0.8233,0.0317</t>
-  </si>
-  <si>
-    <t>0.1416,0.0259,0.8948,0.0045</t>
-  </si>
-  <si>
-    <t>0.2464,0.1507,0.5377,0.0700</t>
-  </si>
-  <si>
-    <t>0.0896,0.3221,0.6302,0.0066</t>
-  </si>
-  <si>
-    <t>0.1888,0.5886,0.1899,0.0050</t>
-  </si>
-  <si>
-    <t>0.4117,0.1022,0.4904,0.0091</t>
-  </si>
-  <si>
-    <t>0.1608,0.0467,0.6224,0.2116</t>
-  </si>
-  <si>
-    <t>0.2390,0.0358,0.7897,0.0204</t>
-  </si>
-  <si>
-    <t>0.5495,0.6311,0.0083,0.0015</t>
-  </si>
-  <si>
-    <t>0.7895,0.3646,0.0063,0.0031</t>
-  </si>
-  <si>
-    <t>0.8893,0.1534,0.0125,0.0048</t>
-  </si>
-  <si>
-    <t>0.9847,0.0081,0.0012,0.0048</t>
-  </si>
-  <si>
-    <t>0.9776,0.0229,0.0023,0.0033</t>
-  </si>
-  <si>
-    <t>0.6053,0.0384,0.3916,0.0158</t>
-  </si>
-  <si>
-    <t>0.8824,0.0357,0.0682,0.0123</t>
-  </si>
-  <si>
-    <t>0.5551,0.0090,0.1296,0.2231</t>
-  </si>
-  <si>
-    <t>0.6925,0.0293,0.2624,0.0266</t>
-  </si>
-  <si>
-    <t>0.6799,0.0143,0.2524,0.0614</t>
-  </si>
-  <si>
-    <t>0.0033,0.0186,0.9695,0.0804</t>
-  </si>
-  <si>
-    <t>0.0016,0.1025,0.9697,0.0208</t>
-  </si>
-  <si>
-    <t>0.0025,0.2856,0.9799,0.0019</t>
-  </si>
-  <si>
-    <t>0.0173,0.2383,0.8958,0.0011</t>
-  </si>
-  <si>
-    <t>0.0111,0.1271,0.9558,0.0010</t>
-  </si>
-  <si>
-    <t>0.9776,0.0074,0.0007,0.0105</t>
-  </si>
-  <si>
-    <t>0.9849,0.0073,0.0031,0.0030</t>
-  </si>
-  <si>
-    <t>0.9515,0.0279,0.0102,0.0156</t>
-  </si>
-  <si>
-    <t>0.9868,0.0081,0.0027,0.0018</t>
-  </si>
-  <si>
-    <t>0.9769,0.0260,0.0013,0.0028</t>
-  </si>
-  <si>
-    <t>0.9832,0.0052,0.0011,0.0067</t>
-  </si>
-  <si>
-    <t>0.9849,0.0047,0.0018,0.0054</t>
-  </si>
-  <si>
-    <t>0.9625,0.0054,0.0069,0.0200</t>
-  </si>
-  <si>
-    <t>0.2459,0.0757,0.7614,0.0246</t>
-  </si>
-  <si>
-    <t>0.2170,0.5700,0.1917,0.0363</t>
-  </si>
-  <si>
-    <t>0.4343,0.0166,0.4931,0.0795</t>
-  </si>
-  <si>
-    <t>0.0012,0.0116,0.9952,0.0020</t>
-  </si>
-  <si>
-    <t>0.0013,0.0094,0.9958,0.0012</t>
-  </si>
-  <si>
-    <t>0.0269,0.1016,0.9233,0.0051</t>
-  </si>
-  <si>
-    <t>0.0035,0.0081,0.9947,0.0007</t>
-  </si>
-  <si>
-    <t>0.0316,0.0219,0.9205,0.0153</t>
-  </si>
-  <si>
-    <t>0.0049,0.0077,0.9937,0.0005</t>
-  </si>
-  <si>
-    <t>0.0188,0.0481,0.9406,0.0164</t>
-  </si>
-  <si>
-    <t>0.0350,0.0724,0.8702,0.0406</t>
-  </si>
-  <si>
-    <t>0.7817,0.0117,0.2362,0.0232</t>
-  </si>
-  <si>
-    <t>0.6745,0.0035,0.3760,0.0199</t>
-  </si>
-  <si>
-    <t>0.7895,0.0228,0.1841,0.0281</t>
-  </si>
-  <si>
-    <t>0.9826,0.0041,0.0003,0.0095</t>
-  </si>
-  <si>
-    <t>0.9916,0.0049,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9936,0.0047,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9827,0.0116,0.0009,0.0044</t>
-  </si>
-  <si>
-    <t>0.9865,0.0020,0.0002,0.0100</t>
-  </si>
-  <si>
-    <t>0.9828,0.0072,0.0047,0.0037</t>
-  </si>
-  <si>
-    <t>0.9824,0.0124,0.0014,0.0042</t>
-  </si>
-  <si>
-    <t>0.9831,0.0070,0.0009,0.0068</t>
-  </si>
-  <si>
-    <t>0.0088,0.4275,0.8786,0.0033</t>
-  </si>
-  <si>
-    <t>0.0013,0.7383,0.9730,0.0018</t>
-  </si>
-  <si>
-    <t>0.0212,0.0987,0.9431,0.0142</t>
-  </si>
-  <si>
-    <t>0.0123,0.2626,0.9004,0.0070</t>
-  </si>
-  <si>
-    <t>0.0088,0.0079,0.9816,0.0078</t>
-  </si>
-  <si>
-    <t>0.0282,0.0170,0.7769,0.5257</t>
-  </si>
-  <si>
-    <t>0.0145,0.1496,0.8879,0.0758</t>
-  </si>
-  <si>
-    <t>0.0962,0.0888,0.8160,0.0660</t>
-  </si>
-  <si>
-    <t>0.8525,0.0024,0.0070,0.1695</t>
-  </si>
-  <si>
-    <t>0.0061,0.0680,0.0008,0.9946</t>
-  </si>
-  <si>
-    <t>0.0549,0.0033,0.0130,0.9594</t>
-  </si>
-  <si>
-    <t>0.0012,0.0012,0.0051,0.9978</t>
-  </si>
-  <si>
-    <t>0.0016,0.0018,0.0008,0.9985</t>
-  </si>
-  <si>
-    <t>0.9275,0.0101,0.0164,0.0281</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.4311,0.0153,0.0332,0.5744</t>
+  </si>
+  <si>
+    <t>0.0084,0.0052,0.0026,0.9935</t>
+  </si>
+  <si>
+    <t>0.1348,0.0193,0.0138,0.9092</t>
+  </si>
+  <si>
+    <t>0.1403,0.0075,0.0045,0.9312</t>
+  </si>
+  <si>
+    <t>0.9909,0.0025,0.0004,0.0042</t>
+  </si>
+  <si>
+    <t>0.9734,0.0091,0.0025,0.0111</t>
+  </si>
+  <si>
+    <t>0.9852,0.0040,0.0016,0.0052</t>
+  </si>
+  <si>
+    <t>0.9910,0.0034,0.0020,0.0024</t>
+  </si>
+  <si>
+    <t>0.9836,0.0096,0.0022,0.0049</t>
+  </si>
+  <si>
+    <t>0.9739,0.0115,0.0016,0.0087</t>
+  </si>
+  <si>
+    <t>0.9881,0.0034,0.0008,0.0049</t>
+  </si>
+  <si>
+    <t>0.9871,0.0032,0.0009,0.0070</t>
+  </si>
+  <si>
+    <t>0.8764,0.0426,0.0772,0.0032</t>
+  </si>
+  <si>
+    <t>0.3180,0.0711,0.6252,0.0089</t>
+  </si>
+  <si>
+    <t>0.1734,0.0200,0.8520,0.0009</t>
+  </si>
+  <si>
+    <t>0.0217,0.0813,0.9173,0.0024</t>
+  </si>
+  <si>
+    <t>0.7995,0.1255,0.0544,0.0495</t>
+  </si>
+  <si>
+    <t>0.0032,0.9944,0.0042,0.0003</t>
+  </si>
+  <si>
+    <t>0.0304,0.9623,0.0139,0.0084</t>
+  </si>
+  <si>
+    <t>0.6694,0.4572,0.0142,0.0089</t>
+  </si>
+  <si>
+    <t>0.0349,0.9624,0.0082,0.0066</t>
+  </si>
+  <si>
+    <t>0.0060,0.9917,0.0072,0.0006</t>
+  </si>
+  <si>
+    <t>0.5734,0.0374,0.4819,0.0073</t>
+  </si>
+  <si>
+    <t>0.2581,0.0050,0.8212,0.0061</t>
+  </si>
+  <si>
+    <t>0.0050,0.0330,0.9848,0.0074</t>
+  </si>
+  <si>
+    <t>0.0312,0.0274,0.9515,0.0039</t>
+  </si>
+  <si>
+    <t>0.0560,0.0030,0.9563,0.0057</t>
+  </si>
+  <si>
+    <t>0.0571,0.0037,0.9544,0.0026</t>
+  </si>
+  <si>
+    <t>0.0041,0.0031,0.9852,0.0149</t>
+  </si>
+  <si>
+    <t>0.8404,0.2778,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.6079,0.0449,0.4142,0.0093</t>
+  </si>
+  <si>
+    <t>0.0020,0.0071,0.9921,0.0154</t>
+  </si>
+  <si>
+    <t>0.0289,0.9532,0.0736,0.0023</t>
+  </si>
+  <si>
+    <t>0.9039,0.0260,0.0519,0.0186</t>
+  </si>
+  <si>
+    <t>0.2762,0.0343,0.7944,0.0256</t>
+  </si>
+  <si>
+    <t>0.8401,0.1736,0.0280,0.0077</t>
+  </si>
+  <si>
+    <t>0.0506,0.9107,0.1765,0.0038</t>
+  </si>
+  <si>
+    <t>0.0028,0.9638,0.4734,0.0039</t>
+  </si>
+  <si>
+    <t>0.0827,0.0247,0.9090,0.0155</t>
+  </si>
+  <si>
+    <t>0.0776,0.0496,0.8901,0.0025</t>
+  </si>
+  <si>
+    <t>0.0137,0.0053,0.8331,0.3598</t>
+  </si>
+  <si>
+    <t>0.0149,0.0884,0.9735,0.0005</t>
+  </si>
+  <si>
+    <t>0.0258,0.9592,0.0290,0.0012</t>
+  </si>
+  <si>
+    <t>0.0150,0.0193,0.9771,0.0013</t>
+  </si>
+  <si>
+    <t>0.0316,0.4508,0.0434,0.9069</t>
+  </si>
+  <si>
+    <t>0.0005,0.9953,0.0053,0.0191</t>
+  </si>
+  <si>
+    <t>0.0007,0.9946,0.0145,0.0093</t>
+  </si>
+  <si>
+    <t>0.0007,0.9954,0.0176,0.0054</t>
+  </si>
+  <si>
+    <t>0.0039,0.0879,0.9877,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.5538,0.9820,0.0004</t>
+  </si>
+  <si>
+    <t>0.0577,0.0468,0.8929,0.0358</t>
+  </si>
+  <si>
+    <t>0.0036,0.0043,0.9939,0.0013</t>
+  </si>
+  <si>
+    <t>0.0137,0.0270,0.9765,0.0043</t>
+  </si>
+  <si>
+    <t>0.0360,0.0742,0.9176,0.0049</t>
+  </si>
+  <si>
+    <t>0.9561,0.0399,0.0053,0.0073</t>
+  </si>
+  <si>
+    <t>0.9798,0.0044,0.0050,0.0072</t>
+  </si>
+  <si>
+    <t>0.9741,0.0210,0.0048,0.0046</t>
+  </si>
+  <si>
+    <t>0.0439,0.0475,0.9583,0.0120</t>
+  </si>
+  <si>
+    <t>0.9822,0.0049,0.0015,0.0103</t>
+  </si>
+  <si>
+    <t>0.9908,0.0036,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.9810,0.0072,0.0015,0.0088</t>
+  </si>
+  <si>
+    <t>0.0002,0.9898,0.9113,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.2137,0.9685,0.0015</t>
+  </si>
+  <si>
+    <t>0.0096,0.0368,0.9774,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9802,0.9795,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0076,0.9952,0.0057</t>
+  </si>
+  <si>
+    <t>0.0090,0.9857,0.0079,0.0016</t>
+  </si>
+  <si>
+    <t>0.0150,0.9850,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.9044,0.0120,0.0710,0.0218</t>
+  </si>
+  <si>
+    <t>0.5765,0.3583,0.0540,0.0049</t>
+  </si>
+  <si>
+    <t>0.0288,0.0711,0.9543,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.9933,0.8780,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9204,0.9302,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9970,0.6291,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9916,0.5708,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.0024,0.0911,0.9767</t>
+  </si>
+  <si>
+    <t>0.0007,0.0267,0.0010,0.9985</t>
+  </si>
+  <si>
+    <t>0.0009,0.0108,0.0020,0.9980</t>
+  </si>
+  <si>
+    <t>0.0013,0.0032,0.0031,0.9978</t>
+  </si>
+  <si>
+    <t>0.0017,0.0022,0.0104,0.9962</t>
+  </si>
+  <si>
+    <t>0.0016,0.0029,0.0036,0.9976</t>
+  </si>
+  <si>
+    <t>0.0002,0.9944,0.7323,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9309,0.9138,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9350,0.8613,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.9528,0.9214,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.9636,0.8703,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9366,0.8783,0.0019</t>
+  </si>
+  <si>
+    <t>0.9920,0.0047,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.9805,0.0126,0.0029,0.0050</t>
+  </si>
+  <si>
+    <t>0.9779,0.0196,0.0023,0.0035</t>
+  </si>
+  <si>
+    <t>0.9881,0.0069,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9828,0.0039,0.0006,0.0090</t>
+  </si>
+  <si>
+    <t>0.9821,0.0111,0.0040,0.0039</t>
+  </si>
+  <si>
+    <t>0.9749,0.0081,0.0013,0.0121</t>
+  </si>
+  <si>
+    <t>0.9869,0.0086,0.0016,0.0022</t>
+  </si>
+  <si>
+    <t>0.9858,0.0028,0.0012,0.0074</t>
+  </si>
+  <si>
+    <t>0.9897,0.0027,0.0006,0.0039</t>
+  </si>
+  <si>
+    <t>0.9893,0.0045,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9938,0.0025,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9871,0.0027,0.0005,0.0069</t>
+  </si>
+  <si>
+    <t>0.9886,0.0050,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.9877,0.0041,0.0006,0.0057</t>
+  </si>
+  <si>
+    <t>0.9886,0.0023,0.0007,0.0061</t>
+  </si>
+  <si>
+    <t>0.0104,0.0070,0.9735,0.0361</t>
+  </si>
+  <si>
+    <t>0.0723,0.0071,0.9456,0.0025</t>
+  </si>
+  <si>
+    <t>0.9315,0.0089,0.0473,0.0028</t>
+  </si>
+  <si>
+    <t>0.0219,0.0054,0.9751,0.0047</t>
+  </si>
+  <si>
+    <t>0.0106,0.9868,0.0021,0.0022</t>
+  </si>
+  <si>
+    <t>0.0079,0.9901,0.0050,0.0012</t>
+  </si>
+  <si>
+    <t>0.0560,0.9560,0.0058,0.0055</t>
+  </si>
+  <si>
+    <t>0.1346,0.8952,0.0260,0.0105</t>
+  </si>
+  <si>
+    <t>0.0084,0.9886,0.0041,0.0015</t>
+  </si>
+  <si>
+    <t>0.0020,0.9965,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.5907,0.5704,0.0059,0.0070</t>
+  </si>
+  <si>
+    <t>0.3104,0.6426,0.0460,0.0797</t>
+  </si>
+  <si>
+    <t>0.1451,0.0187,0.8611,0.0216</t>
+  </si>
+  <si>
+    <t>0.2343,0.3238,0.3110,0.0472</t>
+  </si>
+  <si>
+    <t>0.5970,0.0473,0.3803,0.0073</t>
+  </si>
+  <si>
+    <t>0.2510,0.2702,0.5023,0.3611</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0084,0.0010</t>
+  </si>
+  <si>
+    <t>0.0007,0.9968,0.0048,0.0045</t>
+  </si>
+  <si>
+    <t>0.0013,0.9932,0.0043,0.0123</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0346,0.0010</t>
+  </si>
+  <si>
+    <t>0.0414,0.9570,0.0465,0.0030</t>
+  </si>
+  <si>
+    <t>0.7685,0.2063,0.0660,0.0060</t>
+  </si>
+  <si>
+    <t>0.8197,0.1532,0.0474,0.0057</t>
+  </si>
+  <si>
+    <t>0.9868,0.0049,0.0052,0.0026</t>
+  </si>
+  <si>
+    <t>0.9908,0.0021,0.0005,0.0035</t>
+  </si>
+  <si>
+    <t>0.9775,0.0034,0.0014,0.0154</t>
+  </si>
+  <si>
+    <t>0.9717,0.0128,0.0044,0.0103</t>
+  </si>
+  <si>
+    <t>0.9871,0.0029,0.0020,0.0042</t>
+  </si>
+  <si>
+    <t>0.9902,0.0021,0.0017,0.0026</t>
+  </si>
+  <si>
+    <t>0.9871,0.0038,0.0012,0.0048</t>
+  </si>
+  <si>
+    <t>0.9732,0.0019,0.0031,0.0153</t>
+  </si>
+  <si>
+    <t>0.0026,0.9041,0.7392,0.0031</t>
+  </si>
+  <si>
+    <t>0.0010,0.8539,0.9365,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.2918,0.9704,0.0028</t>
+  </si>
+  <si>
+    <t>0.0042,0.5401,0.9241,0.0011</t>
+  </si>
+  <si>
+    <t>0.9396,0.0228,0.0239,0.0028</t>
+  </si>
+  <si>
+    <t>0.5640,0.0177,0.5121,0.0206</t>
+  </si>
+  <si>
+    <t>0.3121,0.0063,0.7991,0.0076</t>
+  </si>
+  <si>
+    <t>0.5781,0.0627,0.3563,0.0587</t>
+  </si>
+  <si>
+    <t>0.0219,0.0012,0.0028,0.9886</t>
+  </si>
+  <si>
+    <t>0.0001,0.0161,0.0021,0.9988</t>
+  </si>
+  <si>
+    <t>0.0009,0.0064,0.0035,0.9977</t>
+  </si>
+  <si>
+    <t>0.0011,0.0025,0.0021,0.9984</t>
+  </si>
+  <si>
+    <t>0.0021,0.9733,0.5065,0.0012</t>
+  </si>
+  <si>
+    <t>0.9859,0.0033,0.0011,0.0056</t>
+  </si>
+  <si>
+    <t>0.1895,0.8617,0.0090,0.0251</t>
+  </si>
+  <si>
+    <t>0.9880,0.0029,0.0020,0.0040</t>
+  </si>
+  <si>
+    <t>0.9086,0.0861,0.0286,0.0134</t>
+  </si>
+  <si>
+    <t>0.9873,0.0023,0.0006,0.0062</t>
+  </si>
+  <si>
+    <t>0.4861,0.0239,0.0367,0.5862</t>
+  </si>
+  <si>
+    <t>0.9400,0.0143,0.0040,0.0487</t>
+  </si>
+  <si>
+    <t>0.0022,0.0406,0.9822,0.0287</t>
+  </si>
+  <si>
+    <t>0.8222,0.0040,0.0206,0.1465</t>
+  </si>
+  <si>
+    <t>0.5703,0.0073,0.0198,0.5211</t>
+  </si>
+  <si>
+    <t>0.3112,0.5639,0.1513,0.1086</t>
+  </si>
+  <si>
+    <t>0.9473,0.0197,0.0047,0.0205</t>
+  </si>
+  <si>
+    <t>0.9279,0.0611,0.0119,0.0077</t>
+  </si>
+  <si>
+    <t>0.3778,0.5777,0.0594,0.0410</t>
+  </si>
+  <si>
+    <t>0.9055,0.0555,0.0339,0.0044</t>
+  </si>
+  <si>
+    <t>0.9575,0.0231,0.0057,0.0079</t>
+  </si>
+  <si>
+    <t>0.9860,0.0033,0.0012,0.0068</t>
+  </si>
+  <si>
+    <t>0.9860,0.0035,0.0008,0.0072</t>
+  </si>
+  <si>
+    <t>0.9864,0.0031,0.0012,0.0054</t>
+  </si>
+  <si>
+    <t>0.9822,0.0017,0.0017,0.0112</t>
+  </si>
+  <si>
+    <t>0.9898,0.0024,0.0039,0.0020</t>
+  </si>
+  <si>
+    <t>0.9752,0.0040,0.0039,0.0123</t>
+  </si>
+  <si>
+    <t>0.9711,0.0043,0.0046,0.0148</t>
+  </si>
+  <si>
+    <t>0.9900,0.0009,0.0005,0.0051</t>
+  </si>
+  <si>
+    <t>0.3152,0.6897,0.0854,0.0174</t>
+  </si>
+  <si>
+    <t>0.9111,0.0901,0.0098,0.0151</t>
+  </si>
+  <si>
+    <t>0.8736,0.1429,0.0315,0.0072</t>
+  </si>
+  <si>
+    <t>0.4614,0.2743,0.3991,0.0160</t>
+  </si>
+  <si>
+    <t>0.9671,0.0176,0.0010,0.0112</t>
+  </si>
+  <si>
+    <t>0.9398,0.0150,0.0155,0.0239</t>
+  </si>
+  <si>
+    <t>0.9659,0.0135,0.0067,0.0101</t>
+  </si>
+  <si>
+    <t>0.9397,0.0437,0.0074,0.0183</t>
+  </si>
+  <si>
+    <t>0.0044,0.0183,0.9941,0.0024</t>
+  </si>
+  <si>
+    <t>0.9692,0.0141,0.0160,0.0030</t>
+  </si>
+  <si>
+    <t>0.0006,0.0206,0.9959,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.3210,0.9902,0.0016</t>
+  </si>
+  <si>
+    <t>0.0194,0.0054,0.9446,0.0939</t>
+  </si>
+  <si>
+    <t>0.0019,0.5475,0.9738,0.0006</t>
+  </si>
+  <si>
+    <t>0.0096,0.0151,0.9800,0.0057</t>
+  </si>
+  <si>
+    <t>0.0047,0.0049,0.9892,0.0054</t>
+  </si>
+  <si>
+    <t>0.0073,0.0132,0.9849,0.0054</t>
+  </si>
+  <si>
+    <t>0.1030,0.0080,0.8875,0.0210</t>
+  </si>
+  <si>
+    <t>0.0894,0.0079,0.9416,0.0034</t>
+  </si>
+  <si>
+    <t>0.5265,0.3278,0.1543,0.0371</t>
+  </si>
+  <si>
+    <t>0.1639,0.6477,0.1345,0.0071</t>
+  </si>
+  <si>
+    <t>0.1273,0.2785,0.6015,0.0055</t>
+  </si>
+  <si>
+    <t>0.7862,0.0702,0.1421,0.0227</t>
+  </si>
+  <si>
+    <t>0.1927,0.0686,0.6361,0.1135</t>
+  </si>
+  <si>
+    <t>0.1098,0.0269,0.8236,0.0272</t>
+  </si>
+  <si>
+    <t>0.6928,0.4197,0.0188,0.0061</t>
+  </si>
+  <si>
+    <t>0.8653,0.1999,0.0087,0.0045</t>
+  </si>
+  <si>
+    <t>0.9086,0.1031,0.0174,0.0055</t>
+  </si>
+  <si>
+    <t>0.9801,0.0202,0.0032,0.0025</t>
+  </si>
+  <si>
+    <t>0.9335,0.1058,0.0053,0.0066</t>
+  </si>
+  <si>
+    <t>0.6337,0.1968,0.0855,0.0442</t>
+  </si>
+  <si>
+    <t>0.8443,0.0187,0.1597,0.0081</t>
+  </si>
+  <si>
+    <t>0.6136,0.0209,0.0567,0.2548</t>
+  </si>
+  <si>
+    <t>0.8684,0.0106,0.1592,0.0054</t>
+  </si>
+  <si>
+    <t>0.2340,0.0065,0.7042,0.0770</t>
+  </si>
+  <si>
+    <t>0.0020,0.0261,0.9855,0.0149</t>
+  </si>
+  <si>
+    <t>0.0091,0.4073,0.8916,0.0063</t>
+  </si>
+  <si>
+    <t>0.0041,0.2213,0.9714,0.0017</t>
+  </si>
+  <si>
+    <t>0.0291,0.1261,0.9211,0.0030</t>
+  </si>
+  <si>
+    <t>0.0039,0.1391,0.9596,0.0015</t>
+  </si>
+  <si>
+    <t>0.9873,0.0062,0.0012,0.0034</t>
+  </si>
+  <si>
+    <t>0.9835,0.0070,0.0028,0.0043</t>
+  </si>
+  <si>
+    <t>0.9892,0.0053,0.0009,0.0030</t>
+  </si>
+  <si>
+    <t>0.9854,0.0134,0.0014,0.0020</t>
+  </si>
+  <si>
+    <t>0.9831,0.0126,0.0019,0.0025</t>
+  </si>
+  <si>
+    <t>0.9703,0.0269,0.0016,0.0061</t>
+  </si>
+  <si>
+    <t>0.9776,0.0052,0.0082,0.0077</t>
+  </si>
+  <si>
+    <t>0.9799,0.0054,0.0058,0.0066</t>
+  </si>
+  <si>
+    <t>0.0196,0.0091,0.9836,0.0020</t>
+  </si>
+  <si>
+    <t>0.2530,0.2952,0.5312,0.0850</t>
+  </si>
+  <si>
+    <t>0.6627,0.0114,0.2503,0.0618</t>
+  </si>
+  <si>
+    <t>0.0055,0.0399,0.9855,0.0028</t>
+  </si>
+  <si>
+    <t>0.0007,0.0307,0.9933,0.0039</t>
+  </si>
+  <si>
+    <t>0.0197,0.0401,0.9523,0.0058</t>
+  </si>
+  <si>
+    <t>0.0027,0.0146,0.9913,0.0036</t>
+  </si>
+  <si>
+    <t>0.0219,0.0268,0.9492,0.0106</t>
+  </si>
+  <si>
+    <t>0.0029,0.0046,0.9959,0.0007</t>
+  </si>
+  <si>
+    <t>0.0072,0.0137,0.9736,0.0064</t>
+  </si>
+  <si>
+    <t>0.0354,0.4755,0.4835,0.0275</t>
+  </si>
+  <si>
+    <t>0.3376,0.0268,0.5880,0.0845</t>
+  </si>
+  <si>
+    <t>0.6170,0.0146,0.4859,0.0130</t>
+  </si>
+  <si>
+    <t>0.9425,0.0116,0.0328,0.0054</t>
+  </si>
+  <si>
+    <t>0.9864,0.0044,0.0001,0.0050</t>
+  </si>
+  <si>
+    <t>0.9916,0.0032,0.0003,0.0033</t>
+  </si>
+  <si>
+    <t>0.9951,0.0033,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9814,0.0109,0.0035,0.0026</t>
+  </si>
+  <si>
+    <t>0.9872,0.0020,0.0002,0.0104</t>
+  </si>
+  <si>
+    <t>0.9881,0.0082,0.0016,0.0020</t>
+  </si>
+  <si>
+    <t>0.9897,0.0058,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.9833,0.0074,0.0009,0.0070</t>
+  </si>
+  <si>
+    <t>0.0292,0.0741,0.8887,0.0022</t>
+  </si>
+  <si>
+    <t>0.0014,0.3708,0.9816,0.0054</t>
+  </si>
+  <si>
+    <t>0.0075,0.3708,0.9196,0.0046</t>
+  </si>
+  <si>
+    <t>0.0403,0.2168,0.7024,0.0381</t>
+  </si>
+  <si>
+    <t>0.0092,0.0061,0.9824,0.0037</t>
+  </si>
+  <si>
+    <t>0.0555,0.0437,0.8565,0.1846</t>
+  </si>
+  <si>
+    <t>0.0081,0.0195,0.9429,0.1213</t>
+  </si>
+  <si>
+    <t>0.0209,0.0180,0.9536,0.0263</t>
+  </si>
+  <si>
+    <t>0.6433,0.0025,0.0179,0.3631</t>
+  </si>
+  <si>
+    <t>0.0210,0.0165,0.0029,0.9879</t>
+  </si>
+  <si>
+    <t>0.0503,0.0047,0.0053,0.9712</t>
+  </si>
+  <si>
+    <t>0.0022,0.0008,0.0068,0.9967</t>
+  </si>
+  <si>
+    <t>0.0012,0.0015,0.0007,0.9988</t>
+  </si>
+  <si>
+    <t>0.9015,0.0311,0.0221,0.0384</t>
   </si>
 </sst>
 </file>
@@ -1959,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2284,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2382,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2438,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2914,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2990,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3166,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,10 +3883,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3922,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4118,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,10 +4149,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,10 +4541,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4664,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4684,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4902,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,10 +5353,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5434,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
